--- a/bench/data/files/synthetic6_A.xlsx
+++ b/bench/data/files/synthetic6_A.xlsx
@@ -577,17 +577,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Kepler Holdings</t>
+          <t>Echo Partners</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -597,42 +597,42 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>2012-08-25</t>
+          <t>2012-12-14</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2017-10-04</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>804.6</v>
+        <v>1292</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>842.6</v>
+        <v>3969</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>139.6</v>
+        <v>312.1</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>336.8</v>
+        <v>493.7</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>535.6</v>
+        <v>348.2</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.68</v>
+        <v>0.249</v>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>James Hassan, Sophie Brown</t>
+          <t>Thomas Zhang, Jennifer Zhang</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Mosaic GmbH</t>
+          <t>Echo Labs</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -642,58 +642,62 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2011-06-16</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>2010-04-11</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
       <c r="G7" s="5" t="n">
-        <v>334.1</v>
+        <v>1391.4</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v/>
+        <v>1291.8</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>89.7</v>
+        <v>254.8</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v/>
+        <v>312.5</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>142.8</v>
+        <v>528.8</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.858</v>
+        <v>0.523</v>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Daniel Chen, Daniel Lopez, Thomas Chen, Sarah Gupta, Priya Yamamoto</t>
+          <t>Laura Lopez, Emma Brown, David Ivanov</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Vertex AG</t>
+          <t>Apex Group</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Tokyo, JP</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -703,52 +707,52 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2010-03-20</t>
+          <t>2012-03-24</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>2014-04-16</t>
+          <t>2018-05-21</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1734.1</v>
+        <v>1594.9</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>2701.4</v>
+        <v>4080.3</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>165.5</v>
+        <v>294.7</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>353.4</v>
+        <v>505.5</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>569</v>
+        <v>514.8</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.381</v>
+        <v>0.956</v>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>Jessica Chen, Laura Nakamura, Robert Ueno, Thomas Ueno, Jessica Tanaka</t>
+          <t>Mark Hassan, Laura Davis</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Atlas Labs</t>
+          <t>Indigo Health</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -758,47 +762,47 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>2011-12-17</t>
+          <t>2011-02-28</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2017-03-14</t>
+          <t>2015-01-04</t>
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1341</v>
+        <v>1836.8</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1684.4</v>
+        <v>2690.6</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>146.7</v>
+        <v>338.9</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>178.5</v>
+        <v>768.5</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>583.5</v>
+        <v>634.6</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.878</v>
+        <v>0.777</v>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>Hannah Kim, Jessica Qureshi</t>
+          <t>Rachel Chen, Christopher Gupta, Wei Evans, Mark Xu, Jessica Chen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Bloom Networks</t>
+          <t>Cobalt Logic</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -813,181 +817,181 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2012-01-16</t>
+          <t>2012-08-23</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2016-12-05</t>
+          <t>2015-06-07</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1247.3</v>
+        <v>220.5</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>2076.8</v>
+        <v>713</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>155.7</v>
+        <v>38.8</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>287.9</v>
+        <v>89.5</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>527.4</v>
+        <v>147.2</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.746</v>
+        <v>0.419</v>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>James Brown, Sarah Chen, Wei Tanaka</t>
+          <t>Ahmed Tanaka, Ahmed Chen, James Nakamura, Priya Mueller, James Evans</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Nimbus Logistics</t>
+          <t>Helix Solutions</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2013-04-22</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>2021-07-02</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1128</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3111.7</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>255.8</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>475.8</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Elena Mueller, Rachel Kim, Laura Schmidt, Wei Evans</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Drift Media</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>2010-04-08</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2017-04-08</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>100.7</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Andrew Johnson, Amanda Johnson, Priya Ueno, Elena Vega, Sophie Vega</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Paris, FR</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2012-03-07</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1549.1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>3787.4</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>534.3</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Sarah Schmidt, Thomas Rossi, Mark Gupta, Christopher O'Brien</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Fund A Average</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>927</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>1485.1</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="J12" s="7" t="n">
-        <v>236</v>
-      </c>
-      <c r="K12" s="7" t="n">
-        <v>403.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="G13" s="7" t="n">
+        <v>1287.5</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>2806.3</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>486.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Fund B</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Delta Pharma</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>2012-05-18</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2018-03-26</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>1197.1</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>1796.6</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>199.7</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>271</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>211.5</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>Michael Williams, Matthew Kim, Ahmed Yamamoto, Mark Patel</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Lattice Capital</t>
+          <t>Lumen Ltd</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1002,53 +1006,57 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>2013-07-20</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t>2013-02-14</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>2016-11-26</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n">
-        <v>912.9</v>
+        <v>1937.2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v/>
+        <v>6518.1</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>155.6</v>
+        <v>294</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v/>
+        <v>728.1</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>151.8</v>
+        <v>240.7</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.307</v>
+        <v>0.387</v>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Robert Schmidt, Sophie Xu</t>
+          <t>Daniel Yamamoto, Jennifer Lopez, Emma Zhang, Olivia Tanaka</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Umbra Labs</t>
+          <t>Bloom Ltd</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1058,52 +1066,52 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>2013-10-01</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2019-11-28</t>
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>287.5</v>
+        <v>786.4</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>217.5</v>
+        <v>2222.3</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>30.3</v>
+        <v>131.5</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>35.4</v>
+        <v>169.9</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>100</v>
+        <v>378.9</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.881</v>
+        <v>0.654</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t>Jessica Evans, Elena Qureshi, James Evans, Andrew Ivanov, Andrew O'Brien</t>
+          <t>Jennifer Johnson, Sarah Vega, Rachel Anderson, Hannah Nakamura</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Atlas Corp</t>
+          <t>Indigo Networks</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1113,52 +1121,52 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>2013-12-26</t>
+          <t>2013-01-05</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2019-11-18</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1546.7</v>
+        <v>1944.7</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>3140</v>
+        <v>2562.9</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>209.5</v>
+        <v>225.9</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>401.8</v>
+        <v>540.1</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>142.3</v>
+        <v>558.2</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.399</v>
+        <v>0.576</v>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Chen, Ravi Xu, James Vega, Hannah Brown, Michael Chen</t>
+          <t>James Evans, Olivia Williams, Ahmed Davis</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Delta Ltd</t>
+          <t>Vertex Industries</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1168,103 +1176,107 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2013-07-17</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2022-09-07</t>
+          <t>2017-04-20</t>
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>641.4</v>
+        <v>499.8</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>2148.9</v>
+        <v>1347</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>178.1</v>
+        <v>107.2</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>216.1</v>
+        <v>144.6</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>629.4</v>
+        <v>480.7</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.929</v>
+        <v>0.331</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Michael Schmidt, Michael Ivanov, Michael Schmidt, James Xu, Wei Gupta</t>
+          <t>Mark Rossi, Wei Chen, Hannah Gupta, Amanda Rossi, Jessica Lopez</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Wavelength Systems</t>
+          <t>Helix Tech</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>London, UK</t>
+          <t>Atlanta, GA</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>2013-01-20</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr"/>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>2018-04-29</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n">
-        <v>463.6</v>
+        <v>1896.4</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v/>
+        <v>3156.8</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>84.90000000000001</v>
+        <v>316</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v/>
+        <v>653.6</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>110.4</v>
+        <v>876.1</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.707</v>
+        <v>0.318</v>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>Sophie Ivanov, Elena Lopez</t>
+          <t>Robert Hassan, Ahmed Zhang, David Evans</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Kepler Pharma</t>
+          <t>Krypton Health</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Zurich, CH</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1274,52 +1286,52 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>2014-08-01</t>
+          <t>2013-01-22</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2019-10-21</t>
+          <t>2020-11-19</t>
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>174.8</v>
+        <v>1624.2</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>154.9</v>
+        <v>5603.8</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>32</v>
+        <v>397.8</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>66.59999999999999</v>
+        <v>948.8</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>134.1</v>
+        <v>296.3</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.593</v>
+        <v>0.823</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Daniel Patel, Hannah Fischer, Christopher Evans</t>
+          <t>Sarah Ivanov, Yuki Patel, Laura Tanaka, Christopher Mueller</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Ember Pharma</t>
+          <t>Umbra Systems</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Boston, MA</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1329,47 +1341,47 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>2014-08-23</t>
+          <t>2013-08-13</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
+          <t>2018-08-20</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1684.2</v>
+        <v>1921.3</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>4581.1</v>
+        <v>2787.8</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>334.7</v>
+        <v>211.4</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>814.1</v>
+        <v>514.5</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>231</v>
+        <v>317.1</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.219</v>
+        <v>0.896</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Ivanov, Michael Lopez, Matthew Vega</t>
+          <t>Sophie Hassan, Sarah Kim, Christopher Nakamura, Ahmed Johnson</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Tessera Materials</t>
+          <t>Xenith Labs</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1384,296 +1396,296 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>2014-02-17</t>
+          <t>2014-05-05</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2017-12-03</t>
+          <t>2019-05-18</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1738.3</v>
+        <v>153.2</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>3202.1</v>
+        <v>499.9</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>152.2</v>
+        <v>17.9</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>132.7</v>
+        <v>42.6</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>430.9</v>
+        <v>22.3</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.263</v>
+        <v>0.579</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>Andrew Ivanov, Sophie Ivanov, James Anderson, Andrew Schmidt</t>
+          <t>Jessica Nakamura, Emma Davis, David Qureshi, Mark Williams, Daniel Fischer</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Wavelength Bio</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>2013-01-08</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>2017-10-09</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>294.7</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>761.4</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Christopher Gupta, Priya Patel, James Fischer, Sarah Hassan</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Tessera Group</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Seattle, WA</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>2015-08-24</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2018-08-01</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>872.9</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>2141.4</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>217.1</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>382.2</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>682.7</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Priya Johnson, Christopher Ueno, Michael Johnson, Ahmed Vega</t>
-        </is>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Fund B Average</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1345.4</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>3087.3</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>212.7</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>467.8</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>396.3</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Radial Labs</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>New York, NY</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>2012-05-08</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>2017-03-25</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>1418.4</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>3699.2</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>303.2</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>694</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Robert Hassan, Wei Mueller, Laura Gupta, Sarah Nakamura</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Fund C</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Cipher SA</t>
+          <t>Krypton Capital</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
+          <t>Toronto, CA</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1616.9</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>2716.3</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>496.9</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>1553.1</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>James Tanaka, Yuki Nakamura, Jennifer Williams, Yuki Chen, Olivia Zhang</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Forge Industries</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Zurich, CH</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>2024-04-05</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>567.9</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1874.8</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>275.9</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>500.4</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Yuki Johnson, Hannah Rossi, Laura Johnson</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Kepler Group</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Singapore, SG</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2016-03-21</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>2024-01-16</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1176.3</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1834.6</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>172.7</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Yuki Evans, Thomas Evans, Sophie Nakamura, Sarah Lopez</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Apex Health</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
           <t>Seattle, WA</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>2012-10-13</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>2017-10-21</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>728.5</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>1721.4</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>148.6</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>320.9</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Daniel Davis, Emma Williams, Mark Evans, Christopher Rossi</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Fund B Average</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>920.1</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>2142.2</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>162</v>
-      </c>
-      <c r="J28" s="7" t="n">
-        <v>311.2</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>248.8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>Fund C</t>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2017-12-05</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>2021-01-31</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1989.3</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>3819</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>495.1</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>675.2</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Jennifer Fischer, Matthew Patel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Zenith Media</t>
+          <t>Halo AG</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -1688,52 +1700,52 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2014-06-11</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2019-08-12</t>
         </is>
       </c>
       <c r="G31" s="5" t="n">
-        <v>524.2</v>
+        <v>988</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>1200.3</v>
+        <v>2070.4</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>124.9</v>
+        <v>232.6</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>207.2</v>
+        <v>553.3</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>245.7</v>
+        <v>750.6</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.956</v>
+        <v>0.931</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>Thomas Lopez, Ahmed Brown, James Williams</t>
+          <t>Andrew Chen, Robert Schmidt, Thomas Gupta, Elena Qureshi</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Vertex Pharma</t>
+          <t>Iris Corp</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1743,52 +1755,52 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>2015-04-07</t>
+          <t>2017-08-04</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="G32" s="5" t="n">
-        <v>731.8</v>
+        <v>1264.2</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>2072.4</v>
+        <v>1705.8</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>125.4</v>
+        <v>117.3</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>201.3</v>
+        <v>194.3</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>66.5</v>
+        <v>229.2</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.281</v>
+        <v>0.833</v>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>Andrew Fischer, Andrew Schmidt, Ahmed Mueller, Matthew Yamamoto, Sarah Williams</t>
+          <t>Jennifer Xu, Christopher Chen, Christopher O'Brien, Amanda O'Brien</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Mosaic Materials</t>
+          <t>Meridian Industries</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1798,52 +1810,52 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2017-10-09</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1747.7</v>
+        <v>991.2</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>4987.8</v>
+        <v>1571.7</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>197.8</v>
+        <v>152.8</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>481.4</v>
+        <v>376.1</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>677.4</v>
+        <v>516.9</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.749</v>
+        <v>0.411</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>James Chen, Christopher Williams</t>
+          <t>Robert Anderson, Emma Davis</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Atlas Dynamics</t>
+          <t>Iris Group</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1853,52 +1865,52 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>2015-03-22</t>
+          <t>2015-12-14</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2020-12-31</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1288.5</v>
+        <v>1895.9</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>1985.2</v>
+        <v>4946.4</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>145.9</v>
+        <v>374.4</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>252.5</v>
+        <v>891.4</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>337.8</v>
+        <v>234.8</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.92</v>
+        <v>0.342</v>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
-          <t>Rachel O'Brien, Olivia Xu</t>
+          <t>James Davis, David Tanaka, Amanda Davis, Thomas Brown, Daniel Schmidt</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Meridian Group</t>
+          <t>Wavelength Networks</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Austin, TX</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1908,52 +1920,52 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>2016-05-16</t>
+          <t>2014-12-16</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2020-01-05</t>
         </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>233.1</v>
+        <v>1705.8</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>586.8</v>
+        <v>5236</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>58.5</v>
+        <v>243.1</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>140.5</v>
+        <v>391.5</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>111</v>
+        <v>974.1</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.798</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>Robert Xu, Robert Hassan, Christopher Xu</t>
+          <t>Sophie Ivanov, Wei Anderson, Wei Yamamoto, James Kim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Fathom Energy</t>
+          <t>Helix Health</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Paris, FR</t>
+          <t>Munich, DE</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1963,47 +1975,47 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>2014-10-24</t>
+          <t>2015-10-15</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2019-09-15</t>
+          <t>2020-12-12</t>
         </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>162.9</v>
+        <v>508.4</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>315.6</v>
+        <v>1604.3</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>40.9</v>
+        <v>116.5</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>77.09999999999999</v>
+        <v>148.2</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>102.6</v>
+        <v>315.8</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.729</v>
+        <v>0.179</v>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>Emma Qureshi, Ahmed Mueller, Hannah Qureshi, Amanda Davis</t>
+          <t>Elena Chen, Jennifer Fischer, Olivia Ueno, Hannah Zhang, Thomas Gupta</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Kepler Inc</t>
+          <t>Cobalt Labs</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2018,52 +2030,52 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>2015-11-05</t>
+          <t>2014-03-12</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="G37" s="5" t="n">
-        <v>68.5</v>
+        <v>1754.9</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>204.6</v>
+        <v>4619.6</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>8.1</v>
+        <v>364.3</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>17.5</v>
+        <v>434.2</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>32.8</v>
+        <v>643.4</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.761</v>
+        <v>0.742</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>Olivia Vega, Michael Qureshi, Robert Xu, Laura Evans, Elena Kim</t>
+          <t>Yuki Mueller, Mark Tanaka, Jennifer Tanaka, Sophie Nakamura, Olivia Davis</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Atlas Energy</t>
+          <t>Tessera Logic</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2073,52 +2085,52 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>2016-07-01</t>
+          <t>2015-03-06</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2021-07-31</t>
+          <t>2021-05-31</t>
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>211.1</v>
+        <v>1704.6</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>371.1</v>
+        <v>3238</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>57.4</v>
+        <v>363.6</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>68.2</v>
+        <v>653.8</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>159.7</v>
+        <v>1283.6</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.473</v>
+        <v>0.952</v>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
-          <t>Laura Brown, Jessica Patel, Jessica Vega, Matthew Fischer</t>
+          <t>Matthew Vega, Christopher Anderson, Hannah Hassan, Emma Evans, Wei Rossi</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Gravity Capital</t>
+          <t>Quanta SA</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Sydney, AU</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2128,35 +2140,35 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>2015-09-18</t>
+          <t>2017-04-15</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2023-06-22</t>
+          <t>2021-01-18</t>
         </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1783.5</v>
+        <v>1962.5</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>2588</v>
+        <v>2888.9</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>261.4</v>
+        <v>359.1</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>221.8</v>
+        <v>717.2</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>739</v>
+        <v>1339.7</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.738</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>Thomas Schmidt, Sarah O'Brien, Olivia Xu, Christopher Tanaka, Yuki Fischer</t>
+          <t>Laura Evans, Olivia Anderson</t>
         </is>
       </c>
     </row>
@@ -2167,19 +2179,19 @@
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>750.1</v>
+        <v>1394.3</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>1590.2</v>
+        <v>2932.8</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>113.4</v>
+        <v>253.1</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>185.3</v>
+        <v>444.1</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>274.7</v>
+        <v>710.3</v>
       </c>
     </row>
     <row r="42">
@@ -2192,17 +2204,17 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Bloom Dynamics</t>
+          <t>Umbra Foods</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -2212,52 +2224,52 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>2018-12-18</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>482.4</v>
+        <v>803.8</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>835.6</v>
+        <v>646</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>95</v>
+        <v>106.2</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>225.1</v>
+        <v>97.8</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>229</v>
+        <v>153.1</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.949</v>
+        <v>0.866</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>Christopher Mueller, Olivia Xu, Jessica Ivanov, David Schmidt</t>
+          <t>Wei Hassan, Matthew Johnson, James Fischer, Ahmed Rossi</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Stratus Pharma</t>
+          <t>Glacier Pharma</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -2267,107 +2279,103 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>2017-05-08</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2021-03-18</t>
+          <t>2020-02-24</t>
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1923.9</v>
+        <v>464.3</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>4821.3</v>
+        <v>1372.2</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>206.4</v>
+        <v>101.6</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>446.1</v>
+        <v>158.1</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>566</v>
+        <v>108.7</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.582</v>
+        <v>0.573</v>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
-          <t>Laura Chen, James Ueno, Sophie Johnson, Emma O'Brien, David Lopez</t>
+          <t>David Hassan, Sophie Fischer, Priya Nakamura, Jessica Brown</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Tessera Media</t>
+          <t>Stratus Group</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Toronto, CA</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>2017-10-14</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2023-12-30</t>
-        </is>
-      </c>
+          <t>2019-07-28</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="n">
-        <v>973</v>
+        <v>1552.5</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>1017.7</v>
+        <v/>
       </c>
       <c r="I45" s="5" t="n">
-        <v>95.90000000000001</v>
+        <v>207.9</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>187.3</v>
+        <v/>
       </c>
       <c r="K45" s="5" t="n">
-        <v>117.7</v>
+        <v>740.4</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.233</v>
+        <v>0.35</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t>Ravi Ueno, Emma Mueller, Andrew Rossi, Hannah Johnson</t>
+          <t>Elena Ueno, Amanda Nakamura</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Lattice Health</t>
+          <t>Forge Inc</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -2377,52 +2385,52 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>2019-03-23</t>
+          <t>2019-06-08</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="G46" s="5" t="n">
-        <v>386.4</v>
+        <v>1002.3</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>535.9</v>
+        <v>2195.6</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>52.2</v>
+        <v>166.5</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>102.2</v>
+        <v>206.2</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>204.7</v>
+        <v>231.5</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.504</v>
+        <v>0.616</v>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
-          <t>Christopher Gupta, Daniel O'Brien, Elena Rossi</t>
+          <t>Sophie Mueller, Rachel Gupta, Andrew Johnson, Daniel Davis, Elena Ueno</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Ember Systems</t>
+          <t>Atlas SA</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2432,52 +2440,52 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>2019-12-01</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1377.7</v>
+        <v>397.5</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>3505.7</v>
+        <v>995.9</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>148.5</v>
+        <v>59.3</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>225.6</v>
+        <v>132.4</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>304.1</v>
+        <v>106.3</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.605</v>
+        <v>0.378</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>Ravi Ivanov, Emma Williams, Jessica Johnson, Yuki Rossi, Emma Zhang</t>
+          <t>Sarah Ueno, Ravi Evans, Daniel Schmidt, Matthew Schmidt</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Gravity SA</t>
+          <t>Xenith Pharma</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Tokyo, JP</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2487,191 +2495,187 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>2019-01-27</t>
+          <t>2017-06-22</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1905.6</v>
+        <v>766.1</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>4541.1</v>
+        <v>1469.9</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>277.2</v>
+        <v>130.1</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>484</v>
+        <v>208.5</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1091.2</v>
+        <v>466.8</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
-          <t>Priya Xu, Emma Zhang</t>
+          <t>Daniel Anderson, Laura Johnson</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Meridian Foods</t>
+          <t>Yields Holdings</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Realized</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>2016-11-15</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>866.9</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>772</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>Olivia Evans, Robert Mueller, Emma Anderson, Laura Schmidt</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Fund D Average</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>836.2</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>1241.9</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>157</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>289.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Fund E</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Nova SA</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>2017-03-20</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2021-04-19</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>559.8</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="M49" s="5" t="inlineStr">
-        <is>
-          <t>Sarah Nakamura, Wei Johnson, Mark Qureshi, James Davis, Olivia Evans</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Fathom Tech</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Toronto, CA</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Realized</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>2023-05-28</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>1490.6</v>
-      </c>
-      <c r="H50" s="5" t="n">
-        <v>2811.3</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>378.6</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>312.3</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>686.3</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="M50" s="5" t="inlineStr">
-        <is>
-          <t>Michael Kim, Emma Anderson, David Yamamoto, Sophie Yamamoto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Fund D Average</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>1145.5</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>2328.6</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="J51" s="7" t="n">
-        <v>269.1</v>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>419.4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Fund E</t>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>2019-07-12</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="n">
+        <v>1171.7</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>215.8</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>657.2</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>James Gupta, Sophie Tanaka, Sarah Ivanov, Sophie Ivanov</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Cipher Logistics</t>
+          <t>Indigo Dynamics</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -2681,47 +2685,47 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2019-06-27</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1198.8</v>
+        <v>942.6</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>2207.1</v>
+        <v>2468.9</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>238</v>
+        <v>85.3</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>589.2</v>
+        <v>138.8</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>709.7</v>
+        <v>261.8</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.351</v>
+        <v>0.573</v>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
-          <t>Matthew Patel, Matthew Lopez</t>
+          <t>Ahmed Evans, James Xu</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Echo Networks</t>
+          <t>Bloom Dynamics</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -2731,112 +2735,104 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>2021-01-08</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>2025-01-24</t>
-        </is>
-      </c>
+          <t>2020-01-04</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
       <c r="G55" s="5" t="n">
-        <v>808.4</v>
+        <v>1867.2</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>650.7</v>
+        <v/>
       </c>
       <c r="I55" s="5" t="n">
-        <v>201.1</v>
+        <v>522.8</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>317.1</v>
+        <v/>
       </c>
       <c r="K55" s="5" t="n">
-        <v>585.1</v>
+        <v>453.8</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.233</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>Sarah Patel, Thomas Lopez, Priya Gupta</t>
+          <t>Daniel Brown, Olivia Tanaka</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Ember Tech</t>
+          <t>Gravity Tech</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>San Francisco, CA</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>2025-04-20</t>
-        </is>
-      </c>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr"/>
       <c r="G56" s="5" t="n">
-        <v>173.3</v>
+        <v>746.5</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>148</v>
+        <v/>
       </c>
       <c r="I56" s="5" t="n">
-        <v>14.9</v>
+        <v>72.3</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>31.4</v>
+        <v/>
       </c>
       <c r="K56" s="5" t="n">
-        <v>26.4</v>
+        <v>143.1</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.23</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
-          <t>Wei Davis, David Chen, Rachel Lopez</t>
+          <t>Sophie Davis, Daniel Johnson, Matthew Ivanov, Ahmed O'Brien, Amanda Chen</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Stratus Tech</t>
+          <t>Ember Solutions</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>San Francisco, CA</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -2846,52 +2842,52 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>2019-09-28</t>
+          <t>2019-08-13</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1700.2</v>
+        <v>1400.8</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>2878.4</v>
+        <v>2921.7</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>322</v>
+        <v>150.9</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>558.5</v>
+        <v>360</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>568.2</v>
+        <v>146.6</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.312</v>
+        <v>0.773</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
-          <t>Amanda Qureshi, Emma Schmidt</t>
+          <t>Ravi Gupta, Sophie Anderson, Jennifer Yamamoto, Sarah Zhang</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Fathom Logistics</t>
+          <t>Junction Health</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Atlanta, GA</t>
+          <t>Chicago, IL</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -2901,52 +2897,52 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1876.4</v>
+        <v>1904.5</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>6471.2</v>
+        <v>2977.9</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>402.1</v>
+        <v>332.3</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>699.5</v>
+        <v>495.1</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>608.1</v>
+        <v>409.1</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.316</v>
+        <v>0.431</v>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
-          <t>Sophie Fischer, Amanda Zhang</t>
+          <t>Olivia Ivanov, Jennifer Mueller, Hannah Ivanov</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Vertex Energy</t>
+          <t>Quanta Ltd</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Munich, DE</t>
+          <t>Singapore, SG</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -2956,47 +2952,47 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>151</v>
+        <v>602.3</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>299.8</v>
+        <v>736.6</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>32.3</v>
+        <v>81.3</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>55.1</v>
+        <v>163.8</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>124.2</v>
+        <v>271.5</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.415</v>
+        <v>0.59</v>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t>Jennifer Schmidt, Amanda Chen, Sarah Hassan</t>
+          <t>Ravi Nakamura, Mark Lopez, Jennifer Chen</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Apex Partners</t>
+          <t>Forge Networks</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3011,52 +3007,52 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>2019-03-05</t>
+          <t>2018-04-21</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="G60" s="5" t="n">
-        <v>1170.9</v>
+        <v>1481.5</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>3742</v>
+        <v>1961.3</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>154.1</v>
+        <v>155.4</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>140.8</v>
+        <v>232.3</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>222.6</v>
+        <v>606.9</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.59</v>
+        <v>0.784</v>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
-          <t>Ahmed Patel, James Tanaka, Ravi Fischer, Ahmed Mueller, Rachel Patel</t>
+          <t>Laura Tanaka, Sarah Lopez, Amanda Mueller, Ravi Gupta</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Beacon Materials</t>
+          <t>Yields AG</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -3066,107 +3062,103 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>2021-10-22</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1433.8</v>
+        <v>576.5</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>3263.9</v>
+        <v>685.9</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>132.9</v>
+        <v>133.7</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>205.3</v>
+        <v>151.6</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>223.2</v>
+        <v>304.1</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.666</v>
+        <v>0.318</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t>Elena Xu, Priya Gupta, Olivia Davis</t>
+          <t>David Williams, Yuki Vega, Sarah O'Brien, Thomas Nakamura, Laura Williams</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Forge AG</t>
+          <t>Umbra Inc</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Singapore, SG</t>
+          <t>Paris, FR</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>2021-04-08</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>2025-01-13</t>
-        </is>
-      </c>
+          <t>2021-11-12</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
       <c r="G62" s="5" t="n">
-        <v>990.7</v>
+        <v>1901.4</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>1747</v>
+        <v/>
       </c>
       <c r="I62" s="5" t="n">
-        <v>93.59999999999999</v>
+        <v>306.2</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>180.2</v>
+        <v/>
       </c>
       <c r="K62" s="5" t="n">
-        <v>337.3</v>
+        <v>314.2</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.651</v>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
-          <t>Emma Hassan, Jessica Hassan, Wei O'Brien, Rachel Vega</t>
+          <t>Yuki Williams, Elena Fischer</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Cipher Health</t>
+          <t>Glacier Holdings</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3176,35 +3168,35 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2019-10-02</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>148.9</v>
+        <v>1038.5</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>468.5</v>
+        <v>2125.1</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>19</v>
+        <v>256.9</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>46.5</v>
+        <v>505.8</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>34.2</v>
+        <v>1050.9</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.236</v>
+        <v>0.451</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
-          <t>Sarah Gupta, Rachel Xu</t>
+          <t>Priya Chen, Mark Mueller, Yuki Williams, Olivia Qureshi</t>
         </is>
       </c>
     </row>
@@ -3215,19 +3207,19 @@
         </is>
       </c>
       <c r="G64" s="7" t="n">
-        <v>965.2</v>
+        <v>1239.4</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>2187.7</v>
+        <v>1982.5</v>
       </c>
       <c r="I64" s="7" t="n">
-        <v>161</v>
+        <v>210.3</v>
       </c>
       <c r="J64" s="7" t="n">
-        <v>282.4</v>
+        <v>292.5</v>
       </c>
       <c r="K64" s="7" t="n">
-        <v>343.9</v>
+        <v>419.9</v>
       </c>
     </row>
   </sheetData>
